--- a/reports/Debug-purgatory-20260106/For Winter Ending (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260106/For Winter Ending (Prior Year)_Revenue.xlsx
@@ -124,10 +124,10 @@
     <t>T100</t>
   </si>
   <si>
+    <t>T104</t>
+  </si>
+  <si>
     <t>T105</t>
-  </si>
-  <si>
-    <t>T104</t>
   </si>
   <si>
     <t>department</t>
@@ -657,26 +657,26 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D5" s="2">
-        <v>8526.00</v>
+        <v>1263.50</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="C6" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D6" s="2">
-        <v>1263.50</v>
+        <v>945.30</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -690,7 +690,7 @@
         <v>39</v>
       </c>
       <c r="D7" s="2">
-        <v>945.30</v>
+        <v>8526.00</v>
       </c>
     </row>
     <row r="8" spans="1:4">
